--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.41110807935996</v>
+        <v>4.941805062895993</v>
       </c>
       <c r="D2" t="n">
-        <v>28.8907257537797</v>
+        <v>4.694742934989201</v>
       </c>
       <c r="E2" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F2" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.89479460777157</v>
+        <v>3.39540412376288</v>
       </c>
       <c r="D3" t="n">
-        <v>20.86495415073649</v>
+        <v>3.39055504949468</v>
       </c>
       <c r="E3" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F3" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>66.87675231349083</v>
+        <v>10.86747225094226</v>
       </c>
       <c r="D4" t="n">
-        <v>65.18096584793994</v>
+        <v>10.59190695029024</v>
       </c>
       <c r="E4" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F4" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.99187062204652</v>
+        <v>7.473678976082559</v>
       </c>
       <c r="D5" t="n">
-        <v>8.255085490143539</v>
+        <v>1.341451392148325</v>
       </c>
       <c r="E5" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F5" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.228325078106472</v>
+        <v>1.337102825192302</v>
       </c>
       <c r="D6" t="n">
-        <v>11.50661217892183</v>
+        <v>1.869824479074797</v>
       </c>
       <c r="E6" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F6" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>67.49424448809043</v>
+        <v>10.96781472931469</v>
       </c>
       <c r="D7" t="n">
-        <v>26.37989240453253</v>
+        <v>4.286732515736537</v>
       </c>
       <c r="E7" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F7" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>53.85300226676132</v>
+        <v>8.751112868348715</v>
       </c>
       <c r="D8" t="n">
-        <v>19.09906728794665</v>
+        <v>3.10359843429133</v>
       </c>
       <c r="E8" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F8" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>53.7613795807164</v>
+        <v>8.736224181866415</v>
       </c>
       <c r="D9" t="n">
-        <v>46.13333295639375</v>
+        <v>7.496666605413985</v>
       </c>
       <c r="E9" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F9" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>56.75585135122964</v>
+        <v>9.222825844574817</v>
       </c>
       <c r="D10" t="n">
-        <v>12.73513465688956</v>
+        <v>2.069459381744553</v>
       </c>
       <c r="E10" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F10" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>50.6435039188769</v>
+        <v>8.229569386817497</v>
       </c>
       <c r="D11" t="n">
-        <v>9.206898938428861</v>
+        <v>1.49612107749469</v>
       </c>
       <c r="E11" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F11" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>61.95265062443026</v>
+        <v>10.06730572646992</v>
       </c>
       <c r="D12" t="n">
-        <v>14.82611925870726</v>
+        <v>2.40924437953993</v>
       </c>
       <c r="E12" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F12" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>57.33517539236568</v>
+        <v>9.316966001259424</v>
       </c>
       <c r="D13" t="n">
-        <v>19.90346445102841</v>
+        <v>3.234312973292116</v>
       </c>
       <c r="E13" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F13" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>46.5798965450644</v>
+        <v>7.569233188572965</v>
       </c>
       <c r="D14" t="n">
-        <v>47.69489779546449</v>
+        <v>7.75042089176298</v>
       </c>
       <c r="E14" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F14" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.88293708987679</v>
+        <v>8.755977277104979</v>
       </c>
       <c r="D15" t="n">
-        <v>49.56750742093958</v>
+        <v>8.054719955902684</v>
       </c>
       <c r="E15" t="n">
-        <v>16.55139861320963</v>
+        <v>2.689602274646565</v>
       </c>
       <c r="F15" t="n">
-        <v>17.26922672448135</v>
+        <v>2.806249342728219</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
